--- a/data/trans_dic/P19C02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,8; 25,83</t>
+          <t>18,14; 26,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,83; 25,63</t>
+          <t>18,84; 25,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,38; 32,16</t>
+          <t>24,22; 31,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,32; 45,86</t>
+          <t>37,62; 46,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,16; 26,13</t>
+          <t>19,06; 26,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,85; 32,68</t>
+          <t>25,43; 32,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,24; 34,14</t>
+          <t>26,63; 34,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45,06; 51,17</t>
+          <t>44,97; 51,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,83</t>
+          <t>19,57; 25,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,05; 27,96</t>
+          <t>23,0; 28,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,93; 32,28</t>
+          <t>26,63; 31,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,35; 47,64</t>
+          <t>42,47; 47,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,79; 30,69</t>
+          <t>23,27; 30,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,05; 33,43</t>
+          <t>27,06; 33,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,48; 40,45</t>
+          <t>33,61; 40,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,02; 52,04</t>
+          <t>21,79; 52,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,33; 31,82</t>
+          <t>25,26; 31,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,46; 29,36</t>
+          <t>23,39; 29,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,82; 41,78</t>
+          <t>34,9; 41,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,84; 54,57</t>
+          <t>48,7; 54,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,19; 30,19</t>
+          <t>25,49; 30,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,17; 30,65</t>
+          <t>25,98; 30,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,3; 40,23</t>
+          <t>35,05; 40,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,16; 51,85</t>
+          <t>27,87; 51,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,27; 34,44</t>
+          <t>26,54; 34,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,9; 32,25</t>
+          <t>25,1; 32,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,32; 37,4</t>
+          <t>29,67; 38,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,34; 48,45</t>
+          <t>39,59; 48,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,89; 38,0</t>
+          <t>29,91; 37,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,38; 37,88</t>
+          <t>29,69; 37,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,38; 44,58</t>
+          <t>35,76; 44,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,45; 76,05</t>
+          <t>38,49; 77,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,25; 34,74</t>
+          <t>29,2; 34,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,91; 34,17</t>
+          <t>28,84; 34,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,0; 39,63</t>
+          <t>34,0; 39,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,99; 70,88</t>
+          <t>41,01; 67,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,61; 37,37</t>
+          <t>30,69; 37,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,27; 39,09</t>
+          <t>32,46; 39,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,56; 41,35</t>
+          <t>34,46; 41,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,63; 52,83</t>
+          <t>45,55; 52,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,75; 34,45</t>
+          <t>27,63; 34,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,33; 38,73</t>
+          <t>32,26; 39,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,11; 41,57</t>
+          <t>35,15; 41,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,7; 50,74</t>
+          <t>36,86; 50,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,91; 34,64</t>
+          <t>30,04; 34,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,51; 38,07</t>
+          <t>33,38; 38,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,76; 40,67</t>
+          <t>35,87; 40,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,42; 50,28</t>
+          <t>41,68; 50,15</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,9; 30,63</t>
+          <t>26,83; 30,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,84; 31,4</t>
+          <t>27,93; 31,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,01; 36,66</t>
+          <t>32,92; 36,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,83; 47,58</t>
+          <t>34,02; 47,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,81</t>
+          <t>27,3; 30,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,73; 33,05</t>
+          <t>29,37; 32,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,21; 39,06</t>
+          <t>35,29; 38,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,02; 59,53</t>
+          <t>45,82; 58,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,57; 30,16</t>
+          <t>27,63; 30,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,42; 31,81</t>
+          <t>29,25; 31,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,7; 37,32</t>
+          <t>34,8; 37,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,91; 50,97</t>
+          <t>42,19; 50,88</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85041; 123408</t>
+          <t>86703; 125077</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113884; 155013</t>
+          <t>113957; 155201</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127981; 168853</t>
+          <t>127135; 167761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>228120; 280321</t>
+          <t>230002; 284369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>102885; 140324</t>
+          <t>102379; 141361</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>158225; 208060</t>
+          <t>161906; 208423</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>142819; 185849</t>
+          <t>144938; 186278</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>293568; 333395</t>
+          <t>292987; 333323</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>198991; 251955</t>
+          <t>198588; 254156</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>286244; 347197</t>
+          <t>285580; 349954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287970; 345156</t>
+          <t>284745; 341542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>534817; 601640</t>
+          <t>536273; 603013</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>171784; 221620</t>
+          <t>168028; 218407</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>234278; 289526</t>
+          <t>234350; 291132</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273310; 330218</t>
+          <t>274413; 329795</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>256898; 606972</t>
+          <t>254170; 607658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>203694; 255936</t>
+          <t>203146; 256454</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>211095; 264235</t>
+          <t>210506; 265414</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>301659; 361964</t>
+          <t>302347; 361700</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>460228; 514201</t>
+          <t>458954; 513653</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>384478; 460759</t>
+          <t>389057; 459780</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>462187; 541174</t>
+          <t>458685; 538021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>593993; 676938</t>
+          <t>589830; 675404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>615020; 1093423</t>
+          <t>587796; 1091913</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>143204; 187722</t>
+          <t>144653; 189035</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>158345; 205122</t>
+          <t>159661; 208667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161360; 205845</t>
+          <t>163310; 209138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269954; 332465</t>
+          <t>271707; 333288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>174442; 221750</t>
+          <t>174580; 221094</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>206129; 257030</t>
+          <t>201429; 255781</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>210937; 258454</t>
+          <t>207290; 257287</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>354535; 701190</t>
+          <t>354928; 711831</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>330137; 392146</t>
+          <t>329581; 388384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>380069; 449163</t>
+          <t>379168; 450874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>384231; 447844</t>
+          <t>384178; 448170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>659330; 1139968</t>
+          <t>659522; 1089161</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>217227; 265225</t>
+          <t>217833; 267326</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>259637; 314590</t>
+          <t>261187; 315096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>267060; 319447</t>
+          <t>266271; 318628</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>406118; 470174</t>
+          <t>405384; 467932</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>225594; 280081</t>
+          <t>224640; 278694</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>301737; 361453</t>
+          <t>301090; 364891</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>307839; 364514</t>
+          <t>308235; 366694</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>390116; 539364</t>
+          <t>391768; 535178</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>455523; 527552</t>
+          <t>457402; 528308</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>582379; 661560</t>
+          <t>580166; 660427</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>589895; 670786</t>
+          <t>591742; 669958</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>808865; 981832</t>
+          <t>813876; 979448</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>660275; 751819</t>
+          <t>658676; 746373</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>810594; 914182</t>
+          <t>813097; 915239</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>879600; 976764</t>
+          <t>877134; 974335</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1134610; 1595896</t>
+          <t>1140942; 1588859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>754103; 843476</t>
+          <t>747514; 844575</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>935900; 1040413</t>
+          <t>924557; 1035890</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1009448; 1119982</t>
+          <t>1011762; 1112294</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1646831; 2130632</t>
+          <t>1639898; 2089353</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1431757; 1566168</t>
+          <t>1434830; 1562899</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1782601; 1927511</t>
+          <t>1772288; 1921758</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1919510; 2064428</t>
+          <t>1924967; 2070108</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2905594; 3533389</t>
+          <t>2925284; 3527322</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 26,18</t>
+          <t>17,82; 25,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,84; 25,66</t>
+          <t>18,43; 25,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,22; 31,95</t>
+          <t>24,49; 32,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,62; 46,52</t>
+          <t>38,91; 47,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 26,32</t>
+          <t>19,26; 26,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,43; 32,73</t>
+          <t>24,86; 32,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,63; 34,22</t>
+          <t>26,28; 34,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,97; 51,16</t>
+          <t>45,55; 51,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,57; 25,04</t>
+          <t>19,78; 24,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 28,18</t>
+          <t>23,04; 28,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,63; 31,94</t>
+          <t>26,43; 31,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,47; 47,75</t>
+          <t>43,54; 48,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 30,24</t>
+          <t>23,4; 30,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,06; 33,62</t>
+          <t>27,3; 33,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,61; 40,4</t>
+          <t>33,25; 40,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,79; 52,09</t>
+          <t>47,81; 54,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,26; 31,89</t>
+          <t>25,42; 32,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,39; 29,49</t>
+          <t>23,61; 29,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,9; 41,75</t>
+          <t>34,99; 41,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,7; 54,51</t>
+          <t>48,97; 54,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,49; 30,12</t>
+          <t>25,46; 30,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,98; 30,47</t>
+          <t>26,34; 30,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,05; 40,14</t>
+          <t>35,08; 40,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,87; 51,78</t>
+          <t>49,39; 53,65</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,54; 34,68</t>
+          <t>26,04; 34,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,1; 32,81</t>
+          <t>25,06; 32,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,67; 38,0</t>
+          <t>28,67; 37,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,59; 48,57</t>
+          <t>39,56; 47,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,91; 37,88</t>
+          <t>29,68; 37,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,69; 37,7</t>
+          <t>30,36; 37,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,76; 44,38</t>
+          <t>36,01; 44,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,49; 77,2</t>
+          <t>39,46; 45,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,2; 34,41</t>
+          <t>28,89; 34,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,84; 34,3</t>
+          <t>28,78; 34,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,0; 39,66</t>
+          <t>34,18; 39,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,01; 67,72</t>
+          <t>40,56; 45,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,69; 37,67</t>
+          <t>30,52; 37,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,46; 39,16</t>
+          <t>32,66; 39,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,46; 41,24</t>
+          <t>34,49; 41,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,55; 52,58</t>
+          <t>45,28; 52,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,63; 34,28</t>
+          <t>27,8; 34,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,26; 39,1</t>
+          <t>32,35; 38,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,15; 41,82</t>
+          <t>35,21; 41,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,86; 50,35</t>
+          <t>46,77; 52,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,04; 34,69</t>
+          <t>29,88; 34,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,38; 38,0</t>
+          <t>33,28; 37,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,87; 40,62</t>
+          <t>35,67; 40,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,68; 50,15</t>
+          <t>47,06; 51,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,83; 30,41</t>
+          <t>26,88; 30,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,93; 31,43</t>
+          <t>27,83; 31,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,92; 36,57</t>
+          <t>32,97; 36,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,02; 47,37</t>
+          <t>45,16; 49,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,3; 30,85</t>
+          <t>27,48; 30,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,37; 32,9</t>
+          <t>29,4; 32,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,29; 38,79</t>
+          <t>35,27; 39,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,82; 58,38</t>
+          <t>47,25; 50,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,63; 30,1</t>
+          <t>27,61; 30,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,25; 31,71</t>
+          <t>29,34; 31,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,8; 37,42</t>
+          <t>34,79; 37,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,19; 50,88</t>
+          <t>46,59; 49,1</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255632</t>
+          <t>283399</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>313992</t>
+          <t>345113</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>569624</t>
+          <t>628512</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86703; 125077</t>
+          <t>85149; 121132</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113957; 155201</t>
+          <t>111491; 153179</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127135; 167761</t>
+          <t>128559; 170846</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230002; 284369</t>
+          <t>256638; 312018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>102379; 141361</t>
+          <t>103421; 140633</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>161906; 208423</t>
+          <t>158265; 206720</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>144938; 186278</t>
+          <t>143085; 186129</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>292987; 333323</t>
+          <t>321648; 365952</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>198588; 254156</t>
+          <t>200731; 251151</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>285580; 349954</t>
+          <t>286109; 347798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>284745; 341542</t>
+          <t>282640; 340853</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>536273; 603013</t>
+          <t>594588; 667715</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>467618</t>
+          <t>519411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>486532</t>
+          <t>545325</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>954150</t>
+          <t>1064736</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>168028; 218407</t>
+          <t>169005; 222540</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>234350; 291132</t>
+          <t>236395; 291296</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>274413; 329795</t>
+          <t>271420; 331571</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254170; 607658</t>
+          <t>485893; 557900</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>203146; 256454</t>
+          <t>204473; 258228</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>210506; 265414</t>
+          <t>212481; 267322</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>302347; 361700</t>
+          <t>303139; 362788</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>458954; 513653</t>
+          <t>513093; 570324</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>389057; 459780</t>
+          <t>388617; 459510</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>458685; 538021</t>
+          <t>465130; 540585</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>589830; 675404</t>
+          <t>590356; 674734</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>587796; 1091913</t>
+          <t>1019361; 1107355</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301860</t>
+          <t>336340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>491764</t>
+          <t>340230</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>793624</t>
+          <t>676571</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>144653; 189035</t>
+          <t>141919; 186784</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>159661; 208667</t>
+          <t>159400; 207941</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>163310; 209138</t>
+          <t>157773; 205563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>271707; 333288</t>
+          <t>306220; 371049</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>174580; 221094</t>
+          <t>173193; 218758</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>201429; 255781</t>
+          <t>206012; 257626</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>207290; 257287</t>
+          <t>208757; 257272</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>354928; 711831</t>
+          <t>313851; 365488</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>329581; 388384</t>
+          <t>326042; 390617</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>379168; 450874</t>
+          <t>378326; 451438</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>384178; 448170</t>
+          <t>386305; 449577</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>659522; 1089161</t>
+          <t>636558; 719965</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>435504</t>
+          <t>463115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>489922</t>
+          <t>532895</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>925426</t>
+          <t>996011</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>217833; 267326</t>
+          <t>216628; 266236</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>261187; 315096</t>
+          <t>262828; 316968</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>266271; 318628</t>
+          <t>266518; 321335</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>405384; 467932</t>
+          <t>429207; 496390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>224640; 278694</t>
+          <t>225993; 280843</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>301090; 364891</t>
+          <t>301903; 362544</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>308235; 366694</t>
+          <t>308724; 366071</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>391768; 535178</t>
+          <t>503358; 561473</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>457402; 528308</t>
+          <t>454970; 527175</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>580166; 660427</t>
+          <t>578437; 659398</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>591742; 669958</t>
+          <t>588373; 672197</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>813876; 979448</t>
+          <t>952494; 1041084</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1460614</t>
+          <t>1602266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1782210</t>
+          <t>1763564</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3242824</t>
+          <t>3365829</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>658676; 746373</t>
+          <t>659841; 748681</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>813097; 915239</t>
+          <t>810338; 915626</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>877134; 974335</t>
+          <t>878313; 979996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1140942; 1588859</t>
+          <t>1534252; 1669016</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>747514; 844575</t>
+          <t>752463; 845461</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>924557; 1035890</t>
+          <t>925666; 1036465</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1011762; 1112294</t>
+          <t>1011202; 1118218</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1639898; 2089353</t>
+          <t>1713086; 1816654</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1434830; 1562899</t>
+          <t>1433902; 1560556</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1772288; 1921758</t>
+          <t>1778019; 1922867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1924967; 2070108</t>
+          <t>1924204; 2069709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2925284; 3527322</t>
+          <t>3272423; 3448444</t>
         </is>
       </c>
     </row>
